--- a/docs/downloads/2026-09-23/bursa-report-2026-09-23.xlsx
+++ b/docs/downloads/2026-09-23/bursa-report-2026-09-23.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价1.69低于50日均线1.73，RSI 54.6处中性区间，未超买。EMA20与SAR多头信号偏积极，但价格仍受均线压制，信号可靠性中等。</t>
+          <t>现价1.69低于50日均线1.73，RSI 54.6处中性区间，未超买。EMA20与SAR多头叠加T3突破，信号偏多但受均线压制，可靠性中等。</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>现价0.88高于50日均线0.788，EMA20与SAR均呈多头，T3形态突破；但RSI达71.49，已进入超买区，信号可靠性需留意短线过热。</t>
+          <t>现价0.88高于50日均线0.788，EMA20与SAR均呈多头，T3形态突破有效；但RSI达71.49，已进入超买区，信号可靠性偏中性。</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>现价0.59高于50日均线0.487，EMA20与SAR均呈多头，趋势偏强；但RSI达75.95，已进入超买区，短期动能过热，信号可靠性需谨慎看待。</t>
+          <t>RSI达75.95，处超买区；现价0.59高于50日均线0.487约21%，EMA20与SAR多头信号一致，但短线过热。</t>
         </is>
       </c>
     </row>
@@ -6417,9 +6417,9 @@
       <c r="H131" t="n">
         <v>59.48</v>
       </c>
-      <c r="I131" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">

--- a/docs/downloads/2026-09-23/bursa-report-2026-09-23.xlsx
+++ b/docs/downloads/2026-09-23/bursa-report-2026-09-23.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-23" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-23'!$A$1:$M$285</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-23'!$A$1:$M$284</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M285"/>
+  <dimension ref="A1:M284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价1.69低于50日均线1.73，RSI 54.6处中性区间，未超买。EMA20与SAR多头叠加T3突破，信号偏多但受均线压制，可靠性中等。</t>
+          <t>现价1.69低于50日均线1.73，RSI 54.6处中性区间，未超买；EMA20与SAR多头及T3突破信号偏积极，但均线位置显示上方仍有压力。</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>RSI达75.95，处超买区；现价0.59高于50日均线0.487约21%，EMA20与SAR多头信号一致，但短线过热。</t>
+          <t>RSI达75.95，处超买区；现价0.59高于50日均线0.487约21%，EMA20与SAR多头信号一致，但短线偏热。</t>
         </is>
       </c>
     </row>
@@ -11389,39 +11389,39 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>5338</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>DXN</t>
+          <t>PARADIGM</t>
         </is>
       </c>
       <c r="D242" s="9" t="n">
-        <v>0.465</v>
+        <v>0.825</v>
       </c>
       <c r="E242" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F242" s="11" t="n">
-        <v>1011800</v>
+        <v>1004100</v>
       </c>
       <c r="G242" s="12" t="n">
-        <v>0.36</v>
+        <v>1.79</v>
       </c>
       <c r="H242" t="n">
-        <v>54.09</v>
-      </c>
-      <c r="I242" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.77</v>
+      </c>
+      <c r="I242" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J242" s="9" t="n">
-        <v>0.463</v>
+        <v>0.845</v>
       </c>
       <c r="K242" s="9" t="n">
-        <v>0.461</v>
+        <v>0.881</v>
       </c>
       <c r="L242" t="inlineStr"/>
       <c r="M242" s="14" t="inlineStr"/>
@@ -11434,39 +11434,39 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>0317</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>PARADIGM</t>
+          <t>EPB</t>
         </is>
       </c>
       <c r="D243" s="9" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E243" s="17" t="n">
-        <v>0</v>
+        <v>0.21</v>
+      </c>
+      <c r="E243" s="10" t="n">
+        <v>-0.0233</v>
       </c>
       <c r="F243" s="11" t="n">
-        <v>1004100</v>
+        <v>1003000</v>
       </c>
       <c r="G243" s="12" t="n">
-        <v>1.79</v>
+        <v>4.14</v>
       </c>
       <c r="H243" t="n">
-        <v>24.77</v>
-      </c>
-      <c r="I243" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.84</v>
+      </c>
+      <c r="I243" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J243" s="9" t="n">
-        <v>0.845</v>
+        <v>0.224</v>
       </c>
       <c r="K243" s="9" t="n">
-        <v>0.881</v>
+        <v>0.225</v>
       </c>
       <c r="L243" t="inlineStr"/>
       <c r="M243" s="14" t="inlineStr"/>
@@ -11479,39 +11479,39 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>0317</t>
+          <t>0025</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>EPB</t>
+          <t>YBS</t>
         </is>
       </c>
       <c r="D244" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E244" s="10" t="n">
-        <v>-0.0233</v>
+        <v>0.25</v>
+      </c>
+      <c r="E244" s="16" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F244" s="11" t="n">
-        <v>1003000</v>
+        <v>1002700</v>
       </c>
       <c r="G244" s="12" t="n">
-        <v>4.14</v>
+        <v>0.79</v>
       </c>
       <c r="H244" t="n">
-        <v>40.84</v>
-      </c>
-      <c r="I244" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.37</v>
+      </c>
+      <c r="I244" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J244" s="9" t="n">
-        <v>0.224</v>
+        <v>0.264</v>
       </c>
       <c r="K244" s="9" t="n">
-        <v>0.225</v>
+        <v>0.301</v>
       </c>
       <c r="L244" t="inlineStr"/>
       <c r="M244" s="14" t="inlineStr"/>
@@ -11524,39 +11524,39 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>0025</t>
+          <t>4731</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>YBS</t>
+          <t>SCIENTX</t>
         </is>
       </c>
       <c r="D245" s="9" t="n">
-        <v>0.25</v>
+        <v>3.75</v>
       </c>
       <c r="E245" s="16" t="n">
-        <v>0.0204</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F245" s="11" t="n">
-        <v>1002700</v>
+        <v>1002000</v>
       </c>
       <c r="G245" s="12" t="n">
-        <v>0.79</v>
+        <v>0.98</v>
       </c>
       <c r="H245" t="n">
-        <v>41.37</v>
-      </c>
-      <c r="I245" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.54</v>
+      </c>
+      <c r="I245" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J245" s="9" t="n">
-        <v>0.264</v>
+        <v>3.742</v>
       </c>
       <c r="K245" s="9" t="n">
-        <v>0.301</v>
+        <v>3.722</v>
       </c>
       <c r="L245" t="inlineStr"/>
       <c r="M245" s="14" t="inlineStr"/>
@@ -11569,28 +11569,28 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>4731</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>SCIENTX</t>
+          <t>KIPREIT</t>
         </is>
       </c>
       <c r="D246" s="9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="E246" s="16" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.85</v>
+      </c>
+      <c r="E246" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F246" s="11" t="n">
-        <v>1002000</v>
+        <v>1001200</v>
       </c>
       <c r="G246" s="12" t="n">
-        <v>0.98</v>
+        <v>1.31</v>
       </c>
       <c r="H246" t="n">
-        <v>51.54</v>
+        <v>50.62</v>
       </c>
       <c r="I246" s="15" t="inlineStr">
         <is>
@@ -11598,10 +11598,10 @@
         </is>
       </c>
       <c r="J246" s="9" t="n">
-        <v>3.742</v>
+        <v>0.851</v>
       </c>
       <c r="K246" s="9" t="n">
-        <v>3.722</v>
+        <v>0.843</v>
       </c>
       <c r="L246" t="inlineStr"/>
       <c r="M246" s="14" t="inlineStr"/>
@@ -11614,28 +11614,28 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>KIPREIT</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D247" s="9" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E247" s="17" t="n">
-        <v>0</v>
+        <v>0.99</v>
+      </c>
+      <c r="E247" s="10" t="n">
+        <v>-0.005</v>
       </c>
       <c r="F247" s="11" t="n">
-        <v>1001200</v>
+        <v>997500</v>
       </c>
       <c r="G247" s="12" t="n">
-        <v>1.31</v>
+        <v>0.44</v>
       </c>
       <c r="H247" t="n">
-        <v>50.62</v>
+        <v>46.18</v>
       </c>
       <c r="I247" s="15" t="inlineStr">
         <is>
@@ -11643,10 +11643,10 @@
         </is>
       </c>
       <c r="J247" s="9" t="n">
-        <v>0.851</v>
+        <v>1</v>
       </c>
       <c r="K247" s="9" t="n">
-        <v>0.843</v>
+        <v>1.017</v>
       </c>
       <c r="L247" t="inlineStr"/>
       <c r="M247" s="14" t="inlineStr"/>
@@ -11659,39 +11659,39 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>BURSA</t>
         </is>
       </c>
       <c r="D248" s="9" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="E248" s="10" t="n">
-        <v>-0.005</v>
+        <v>8.1</v>
+      </c>
+      <c r="E248" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F248" s="11" t="n">
-        <v>997500</v>
+        <v>967100</v>
       </c>
       <c r="G248" s="12" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="H248" t="n">
-        <v>46.18</v>
-      </c>
-      <c r="I248" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.88</v>
+      </c>
+      <c r="I248" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J248" s="9" t="n">
-        <v>1</v>
+        <v>8.365</v>
       </c>
       <c r="K248" s="9" t="n">
-        <v>1.017</v>
+        <v>8.451000000000001</v>
       </c>
       <c r="L248" t="inlineStr"/>
       <c r="M248" s="14" t="inlineStr"/>
@@ -11704,39 +11704,39 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>BURSA</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D249" s="9" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="E249" s="17" t="n">
-        <v>0</v>
+        <v>1.11</v>
+      </c>
+      <c r="E249" s="16" t="n">
+        <v>0.0091</v>
       </c>
       <c r="F249" s="11" t="n">
-        <v>967100</v>
+        <v>942100</v>
       </c>
       <c r="G249" s="12" t="n">
-        <v>0.46</v>
+        <v>0.33</v>
       </c>
       <c r="H249" t="n">
-        <v>35.88</v>
-      </c>
-      <c r="I249" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.8</v>
+      </c>
+      <c r="I249" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J249" s="9" t="n">
-        <v>8.365</v>
+        <v>1.104</v>
       </c>
       <c r="K249" s="9" t="n">
-        <v>8.451000000000001</v>
+        <v>1.119</v>
       </c>
       <c r="L249" t="inlineStr"/>
       <c r="M249" s="14" t="inlineStr"/>
@@ -11749,39 +11749,39 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>3255</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>HEIM</t>
         </is>
       </c>
       <c r="D250" s="9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E250" s="16" t="n">
-        <v>0.0091</v>
+        <v>13.4</v>
+      </c>
+      <c r="E250" s="10" t="n">
+        <v>-0.0304</v>
       </c>
       <c r="F250" s="11" t="n">
-        <v>942100</v>
+        <v>903900</v>
       </c>
       <c r="G250" s="12" t="n">
-        <v>0.33</v>
+        <v>1.86</v>
       </c>
       <c r="H250" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="I250" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>18.28</v>
+      </c>
+      <c r="I250" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J250" s="9" t="n">
-        <v>1.104</v>
+        <v>14.532</v>
       </c>
       <c r="K250" s="9" t="n">
-        <v>1.119</v>
+        <v>16.318</v>
       </c>
       <c r="L250" t="inlineStr"/>
       <c r="M250" s="14" t="inlineStr"/>
@@ -11794,39 +11794,39 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>HEIM</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D251" s="9" t="n">
-        <v>13.4</v>
+        <v>1.47</v>
       </c>
       <c r="E251" s="10" t="n">
-        <v>-0.0304</v>
+        <v>-0.0134</v>
       </c>
       <c r="F251" s="11" t="n">
-        <v>903900</v>
+        <v>895600</v>
       </c>
       <c r="G251" s="12" t="n">
-        <v>1.86</v>
+        <v>0.08</v>
       </c>
       <c r="H251" t="n">
-        <v>18.28</v>
-      </c>
-      <c r="I251" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.56</v>
+      </c>
+      <c r="I251" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J251" s="9" t="n">
-        <v>14.532</v>
+        <v>1.47</v>
       </c>
       <c r="K251" s="9" t="n">
-        <v>16.318</v>
+        <v>1.473</v>
       </c>
       <c r="L251" t="inlineStr"/>
       <c r="M251" s="14" t="inlineStr"/>
@@ -11839,39 +11839,39 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D252" s="9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="E252" s="10" t="n">
-        <v>-0.0134</v>
+        <v>0.93</v>
+      </c>
+      <c r="E252" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F252" s="11" t="n">
-        <v>895600</v>
+        <v>876500</v>
       </c>
       <c r="G252" s="12" t="n">
-        <v>0.08</v>
+        <v>0.39</v>
       </c>
       <c r="H252" t="n">
-        <v>50.56</v>
-      </c>
-      <c r="I252" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.83</v>
+      </c>
+      <c r="I252" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J252" s="9" t="n">
-        <v>1.47</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="K252" s="9" t="n">
-        <v>1.473</v>
+        <v>0.957</v>
       </c>
       <c r="L252" t="inlineStr"/>
       <c r="M252" s="14" t="inlineStr"/>
@@ -11884,28 +11884,28 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>YTLREIT</t>
         </is>
       </c>
       <c r="D253" s="9" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E253" s="17" t="n">
-        <v>0</v>
+        <v>0.99</v>
+      </c>
+      <c r="E253" s="10" t="n">
+        <v>-0.005</v>
       </c>
       <c r="F253" s="11" t="n">
-        <v>876500</v>
+        <v>860000</v>
       </c>
       <c r="G253" s="12" t="n">
-        <v>0.39</v>
+        <v>1.57</v>
       </c>
       <c r="H253" t="n">
-        <v>46.83</v>
+        <v>35.92</v>
       </c>
       <c r="I253" s="13" t="inlineStr">
         <is>
@@ -11913,10 +11913,10 @@
         </is>
       </c>
       <c r="J253" s="9" t="n">
-        <v>0.9330000000000001</v>
+        <v>1.001</v>
       </c>
       <c r="K253" s="9" t="n">
-        <v>0.957</v>
+        <v>1.005</v>
       </c>
       <c r="L253" t="inlineStr"/>
       <c r="M253" s="14" t="inlineStr"/>
@@ -11929,28 +11929,28 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>YTLREIT</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D254" s="9" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="E254" s="10" t="n">
-        <v>-0.005</v>
+        <v>1.74</v>
+      </c>
+      <c r="E254" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F254" s="11" t="n">
-        <v>860000</v>
+        <v>844400</v>
       </c>
       <c r="G254" s="12" t="n">
-        <v>1.57</v>
+        <v>0.41</v>
       </c>
       <c r="H254" t="n">
-        <v>35.92</v>
+        <v>44.07</v>
       </c>
       <c r="I254" s="13" t="inlineStr">
         <is>
@@ -11958,10 +11958,10 @@
         </is>
       </c>
       <c r="J254" s="9" t="n">
-        <v>1.001</v>
+        <v>1.768</v>
       </c>
       <c r="K254" s="9" t="n">
-        <v>1.005</v>
+        <v>1.867</v>
       </c>
       <c r="L254" t="inlineStr"/>
       <c r="M254" s="14" t="inlineStr"/>
@@ -11974,39 +11974,39 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D255" s="9" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="E255" s="17" t="n">
-        <v>0</v>
+        <v>3.22</v>
+      </c>
+      <c r="E255" s="10" t="n">
+        <v>-0.0031</v>
       </c>
       <c r="F255" s="11" t="n">
-        <v>844400</v>
+        <v>843900</v>
       </c>
       <c r="G255" s="12" t="n">
-        <v>0.41</v>
+        <v>0.28</v>
       </c>
       <c r="H255" t="n">
-        <v>44.07</v>
-      </c>
-      <c r="I255" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.84999999999999</v>
+      </c>
+      <c r="I255" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J255" s="9" t="n">
-        <v>1.768</v>
+        <v>2.816</v>
       </c>
       <c r="K255" s="9" t="n">
-        <v>1.867</v>
+        <v>2.443</v>
       </c>
       <c r="L255" t="inlineStr"/>
       <c r="M255" s="14" t="inlineStr"/>
@@ -12019,39 +12019,39 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>0157</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>FOCUSP</t>
         </is>
       </c>
       <c r="D256" s="9" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="E256" s="10" t="n">
-        <v>-0.0031</v>
+        <v>0.51</v>
+      </c>
+      <c r="E256" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F256" s="11" t="n">
-        <v>843900</v>
+        <v>829600</v>
       </c>
       <c r="G256" s="12" t="n">
-        <v>0.28</v>
+        <v>2.83</v>
       </c>
       <c r="H256" t="n">
-        <v>75.84999999999999</v>
-      </c>
-      <c r="I256" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.59</v>
+      </c>
+      <c r="I256" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J256" s="9" t="n">
-        <v>2.816</v>
+        <v>0.511</v>
       </c>
       <c r="K256" s="9" t="n">
-        <v>2.443</v>
+        <v>0.507</v>
       </c>
       <c r="L256" t="inlineStr"/>
       <c r="M256" s="14" t="inlineStr"/>
@@ -12064,39 +12064,39 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>0157</t>
+          <t>0392</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>FOCUSP</t>
+          <t>KEEMING</t>
         </is>
       </c>
       <c r="D257" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E257" s="17" t="n">
-        <v>0</v>
+        <v>2.56</v>
+      </c>
+      <c r="E257" s="16" t="n">
+        <v>0.0119</v>
       </c>
       <c r="F257" s="11" t="n">
-        <v>829600</v>
+        <v>822400</v>
       </c>
       <c r="G257" s="12" t="n">
-        <v>2.83</v>
+        <v>0.89</v>
       </c>
       <c r="H257" t="n">
-        <v>49.59</v>
-      </c>
-      <c r="I257" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.96</v>
+      </c>
+      <c r="I257" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J257" s="9" t="n">
-        <v>0.511</v>
+        <v>2.448</v>
       </c>
       <c r="K257" s="9" t="n">
-        <v>0.507</v>
+        <v>2.245</v>
       </c>
       <c r="L257" t="inlineStr"/>
       <c r="M257" s="14" t="inlineStr"/>
@@ -12109,28 +12109,28 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>0392</t>
+          <t>7100</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>KEEMING</t>
+          <t>UCHITEC</t>
         </is>
       </c>
       <c r="D258" s="9" t="n">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="E258" s="16" t="n">
-        <v>0.0119</v>
+        <v>0.0121</v>
       </c>
       <c r="F258" s="11" t="n">
-        <v>822400</v>
+        <v>787600</v>
       </c>
       <c r="G258" s="12" t="n">
-        <v>0.89</v>
+        <v>3.26</v>
       </c>
       <c r="H258" t="n">
-        <v>59.96</v>
+        <v>28.24</v>
       </c>
       <c r="I258" s="15" t="inlineStr">
         <is>
@@ -12138,10 +12138,10 @@
         </is>
       </c>
       <c r="J258" s="9" t="n">
-        <v>2.448</v>
+        <v>2.603</v>
       </c>
       <c r="K258" s="9" t="n">
-        <v>2.245</v>
+        <v>2.687</v>
       </c>
       <c r="L258" t="inlineStr"/>
       <c r="M258" s="14" t="inlineStr"/>
@@ -12154,39 +12154,39 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>7100</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>UCHITEC</t>
+          <t>SENTRAL</t>
         </is>
       </c>
       <c r="D259" s="9" t="n">
-        <v>2.51</v>
+        <v>0.655</v>
       </c>
       <c r="E259" s="16" t="n">
-        <v>0.0121</v>
+        <v>0.0077</v>
       </c>
       <c r="F259" s="11" t="n">
-        <v>787600</v>
+        <v>774500</v>
       </c>
       <c r="G259" s="12" t="n">
-        <v>3.26</v>
+        <v>1.03</v>
       </c>
       <c r="H259" t="n">
-        <v>28.24</v>
-      </c>
-      <c r="I259" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.4</v>
+      </c>
+      <c r="I259" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J259" s="9" t="n">
-        <v>2.603</v>
+        <v>0.664</v>
       </c>
       <c r="K259" s="9" t="n">
-        <v>2.687</v>
+        <v>0.681</v>
       </c>
       <c r="L259" t="inlineStr"/>
       <c r="M259" s="14" t="inlineStr"/>
@@ -12199,28 +12199,28 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>SENTRAL</t>
+          <t>TEOSENG</t>
         </is>
       </c>
       <c r="D260" s="9" t="n">
-        <v>0.655</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E260" s="16" t="n">
-        <v>0.0077</v>
+        <v>0.0062</v>
       </c>
       <c r="F260" s="11" t="n">
-        <v>774500</v>
+        <v>773200</v>
       </c>
       <c r="G260" s="12" t="n">
-        <v>1.03</v>
+        <v>2.6</v>
       </c>
       <c r="H260" t="n">
-        <v>39.4</v>
+        <v>42.67</v>
       </c>
       <c r="I260" s="13" t="inlineStr">
         <is>
@@ -12228,10 +12228,10 @@
         </is>
       </c>
       <c r="J260" s="9" t="n">
-        <v>0.664</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="K260" s="9" t="n">
-        <v>0.681</v>
+        <v>0.848</v>
       </c>
       <c r="L260" t="inlineStr"/>
       <c r="M260" s="14" t="inlineStr"/>
@@ -12244,28 +12244,28 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>TEOSENG</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="D261" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E261" s="16" t="n">
-        <v>0.0062</v>
+        <v>1.3</v>
+      </c>
+      <c r="E261" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F261" s="11" t="n">
-        <v>773200</v>
+        <v>770400</v>
       </c>
       <c r="G261" s="12" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="H261" t="n">
-        <v>42.67</v>
+        <v>35.96</v>
       </c>
       <c r="I261" s="13" t="inlineStr">
         <is>
@@ -12273,10 +12273,10 @@
         </is>
       </c>
       <c r="J261" s="9" t="n">
-        <v>0.8179999999999999</v>
+        <v>1.324</v>
       </c>
       <c r="K261" s="9" t="n">
-        <v>0.848</v>
+        <v>1.349</v>
       </c>
       <c r="L261" t="inlineStr"/>
       <c r="M261" s="14" t="inlineStr"/>
@@ -12289,39 +12289,39 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>0249</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>LGMS</t>
         </is>
       </c>
       <c r="D262" s="9" t="n">
-        <v>1.3</v>
+        <v>0.51</v>
       </c>
       <c r="E262" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F262" s="11" t="n">
-        <v>770400</v>
+        <v>770000</v>
       </c>
       <c r="G262" s="12" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="H262" t="n">
-        <v>35.96</v>
-      </c>
-      <c r="I262" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.29</v>
+      </c>
+      <c r="I262" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J262" s="9" t="n">
-        <v>1.324</v>
+        <v>0.494</v>
       </c>
       <c r="K262" s="9" t="n">
-        <v>1.349</v>
+        <v>0.494</v>
       </c>
       <c r="L262" t="inlineStr"/>
       <c r="M262" s="14" t="inlineStr"/>
@@ -12334,28 +12334,28 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>0249</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>LGMS</t>
+          <t>UTDPLT</t>
         </is>
       </c>
       <c r="D263" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E263" s="17" t="n">
-        <v>0</v>
+        <v>33.2</v>
+      </c>
+      <c r="E263" s="10" t="n">
+        <v>-0.0101</v>
       </c>
       <c r="F263" s="11" t="n">
-        <v>770000</v>
+        <v>756300</v>
       </c>
       <c r="G263" s="12" t="n">
-        <v>1.72</v>
+        <v>0.68</v>
       </c>
       <c r="H263" t="n">
-        <v>59.29</v>
+        <v>52.23</v>
       </c>
       <c r="I263" s="15" t="inlineStr">
         <is>
@@ -12363,10 +12363,10 @@
         </is>
       </c>
       <c r="J263" s="9" t="n">
-        <v>0.494</v>
+        <v>33.072</v>
       </c>
       <c r="K263" s="9" t="n">
-        <v>0.494</v>
+        <v>33.192</v>
       </c>
       <c r="L263" t="inlineStr"/>
       <c r="M263" s="14" t="inlineStr"/>
@@ -12379,39 +12379,39 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>7035</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>UTDPLT</t>
+          <t>CCK</t>
         </is>
       </c>
       <c r="D264" s="9" t="n">
-        <v>33.2</v>
+        <v>0.88</v>
       </c>
       <c r="E264" s="10" t="n">
-        <v>-0.0101</v>
+        <v>-0.0222</v>
       </c>
       <c r="F264" s="11" t="n">
-        <v>756300</v>
+        <v>741300</v>
       </c>
       <c r="G264" s="12" t="n">
-        <v>0.68</v>
+        <v>1.29</v>
       </c>
       <c r="H264" t="n">
-        <v>52.23</v>
-      </c>
-      <c r="I264" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>23.61</v>
+      </c>
+      <c r="I264" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J264" s="9" t="n">
-        <v>33.072</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="K264" s="9" t="n">
-        <v>33.192</v>
+        <v>1.021</v>
       </c>
       <c r="L264" t="inlineStr"/>
       <c r="M264" s="14" t="inlineStr"/>
@@ -12424,39 +12424,39 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>7035</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>CCK</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D265" s="9" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="E265" s="10" t="n">
-        <v>-0.0222</v>
+        <v>2.38</v>
+      </c>
+      <c r="E265" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F265" s="11" t="n">
-        <v>741300</v>
+        <v>736300</v>
       </c>
       <c r="G265" s="12" t="n">
-        <v>1.29</v>
+        <v>0.72</v>
       </c>
       <c r="H265" t="n">
-        <v>23.61</v>
-      </c>
-      <c r="I265" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.13</v>
+      </c>
+      <c r="I265" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J265" s="9" t="n">
-        <v>0.9340000000000001</v>
+        <v>2.294</v>
       </c>
       <c r="K265" s="9" t="n">
-        <v>1.021</v>
+        <v>2.332</v>
       </c>
       <c r="L265" t="inlineStr"/>
       <c r="M265" s="14" t="inlineStr"/>
@@ -12469,28 +12469,28 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D266" s="9" t="n">
-        <v>2.38</v>
+        <v>0.77</v>
       </c>
       <c r="E266" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F266" s="11" t="n">
-        <v>736300</v>
+        <v>722700</v>
       </c>
       <c r="G266" s="12" t="n">
-        <v>0.72</v>
+        <v>0.29</v>
       </c>
       <c r="H266" t="n">
-        <v>56.13</v>
+        <v>52.46</v>
       </c>
       <c r="I266" s="15" t="inlineStr">
         <is>
@@ -12498,10 +12498,10 @@
         </is>
       </c>
       <c r="J266" s="9" t="n">
-        <v>2.294</v>
+        <v>0.764</v>
       </c>
       <c r="K266" s="9" t="n">
-        <v>2.332</v>
+        <v>0.753</v>
       </c>
       <c r="L266" t="inlineStr"/>
       <c r="M266" s="14" t="inlineStr"/>
@@ -12514,28 +12514,28 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>ECOWLD</t>
         </is>
       </c>
       <c r="D267" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E267" s="17" t="n">
-        <v>0</v>
+        <v>1.93</v>
+      </c>
+      <c r="E267" s="10" t="n">
+        <v>-0.0103</v>
       </c>
       <c r="F267" s="11" t="n">
-        <v>722700</v>
+        <v>686200</v>
       </c>
       <c r="G267" s="12" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="H267" t="n">
-        <v>52.46</v>
+        <v>41.77</v>
       </c>
       <c r="I267" s="15" t="inlineStr">
         <is>
@@ -12543,10 +12543,10 @@
         </is>
       </c>
       <c r="J267" s="9" t="n">
-        <v>0.764</v>
+        <v>1.964</v>
       </c>
       <c r="K267" s="9" t="n">
-        <v>0.753</v>
+        <v>2.032</v>
       </c>
       <c r="L267" t="inlineStr"/>
       <c r="M267" s="14" t="inlineStr"/>
@@ -12559,28 +12559,28 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>7163</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>ECOWLD</t>
+          <t>PJBUMI</t>
         </is>
       </c>
       <c r="D268" s="9" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="E268" s="10" t="n">
-        <v>-0.0103</v>
+        <v>4.05</v>
+      </c>
+      <c r="E268" s="16" t="n">
+        <v>0.01</v>
       </c>
       <c r="F268" s="11" t="n">
-        <v>686200</v>
+        <v>679000</v>
       </c>
       <c r="G268" s="12" t="n">
-        <v>0.38</v>
+        <v>1.05</v>
       </c>
       <c r="H268" t="n">
-        <v>41.77</v>
+        <v>72.36</v>
       </c>
       <c r="I268" s="15" t="inlineStr">
         <is>
@@ -12588,10 +12588,10 @@
         </is>
       </c>
       <c r="J268" s="9" t="n">
-        <v>1.964</v>
+        <v>3.949</v>
       </c>
       <c r="K268" s="9" t="n">
-        <v>2.032</v>
+        <v>3.84</v>
       </c>
       <c r="L268" t="inlineStr"/>
       <c r="M268" s="14" t="inlineStr"/>
@@ -12604,39 +12604,39 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>PJBUMI</t>
+          <t>SAMCHEM</t>
         </is>
       </c>
       <c r="D269" s="9" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="E269" s="16" t="n">
-        <v>0.01</v>
+        <v>0.51</v>
+      </c>
+      <c r="E269" s="10" t="n">
+        <v>-0.0097</v>
       </c>
       <c r="F269" s="11" t="n">
-        <v>679000</v>
+        <v>673000</v>
       </c>
       <c r="G269" s="12" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="H269" t="n">
-        <v>72.36</v>
-      </c>
-      <c r="I269" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46</v>
+      </c>
+      <c r="I269" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J269" s="9" t="n">
-        <v>3.949</v>
+        <v>0.518</v>
       </c>
       <c r="K269" s="9" t="n">
-        <v>3.84</v>
+        <v>0.51</v>
       </c>
       <c r="L269" t="inlineStr"/>
       <c r="M269" s="14" t="inlineStr"/>
@@ -12649,28 +12649,28 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5308</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>SAMCHEM</t>
+          <t>SENFONG</t>
         </is>
       </c>
       <c r="D270" s="9" t="n">
-        <v>0.51</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E270" s="10" t="n">
-        <v>-0.0097</v>
+        <v>-0.0072</v>
       </c>
       <c r="F270" s="11" t="n">
-        <v>673000</v>
+        <v>669300</v>
       </c>
       <c r="G270" s="12" t="n">
-        <v>1.08</v>
+        <v>4.99</v>
       </c>
       <c r="H270" t="n">
-        <v>46</v>
+        <v>45.87</v>
       </c>
       <c r="I270" s="13" t="inlineStr">
         <is>
@@ -12678,10 +12678,10 @@
         </is>
       </c>
       <c r="J270" s="9" t="n">
-        <v>0.518</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="K270" s="9" t="n">
-        <v>0.51</v>
+        <v>0.681</v>
       </c>
       <c r="L270" t="inlineStr"/>
       <c r="M270" s="14" t="inlineStr"/>
@@ -12694,39 +12694,39 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>SENFONG</t>
+          <t>PETRONM</t>
         </is>
       </c>
       <c r="D271" s="9" t="n">
-        <v>0.6850000000000001</v>
+        <v>3.72</v>
       </c>
       <c r="E271" s="10" t="n">
-        <v>-0.0072</v>
+        <v>-0.0462</v>
       </c>
       <c r="F271" s="11" t="n">
-        <v>669300</v>
+        <v>665500</v>
       </c>
       <c r="G271" s="12" t="n">
-        <v>4.99</v>
+        <v>3.09</v>
       </c>
       <c r="H271" t="n">
-        <v>45.87</v>
-      </c>
-      <c r="I271" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.96</v>
+      </c>
+      <c r="I271" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J271" s="9" t="n">
-        <v>0.6929999999999999</v>
+        <v>3.544</v>
       </c>
       <c r="K271" s="9" t="n">
-        <v>0.681</v>
+        <v>3.486</v>
       </c>
       <c r="L271" t="inlineStr"/>
       <c r="M271" s="14" t="inlineStr"/>
@@ -12739,28 +12739,28 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>0326</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>PETRONM</t>
+          <t>SORENTO</t>
         </is>
       </c>
       <c r="D272" s="9" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="E272" s="10" t="n">
-        <v>-0.0462</v>
+        <v>0.655</v>
+      </c>
+      <c r="E272" s="16" t="n">
+        <v>0.0077</v>
       </c>
       <c r="F272" s="11" t="n">
-        <v>665500</v>
+        <v>653900</v>
       </c>
       <c r="G272" s="12" t="n">
-        <v>3.09</v>
+        <v>1.87</v>
       </c>
       <c r="H272" t="n">
-        <v>60.96</v>
+        <v>52.93</v>
       </c>
       <c r="I272" s="15" t="inlineStr">
         <is>
@@ -12768,10 +12768,10 @@
         </is>
       </c>
       <c r="J272" s="9" t="n">
-        <v>3.544</v>
+        <v>0.649</v>
       </c>
       <c r="K272" s="9" t="n">
-        <v>3.486</v>
+        <v>0.645</v>
       </c>
       <c r="L272" t="inlineStr"/>
       <c r="M272" s="14" t="inlineStr"/>
@@ -12784,39 +12784,39 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>0326</t>
+          <t>7198</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>SORENTO</t>
+          <t>DPS</t>
         </is>
       </c>
       <c r="D273" s="9" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E273" s="16" t="n">
-        <v>0.0077</v>
+        <v>0.52</v>
+      </c>
+      <c r="E273" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F273" s="11" t="n">
-        <v>653900</v>
+        <v>608700</v>
       </c>
       <c r="G273" s="12" t="n">
-        <v>1.87</v>
+        <v>1.59</v>
       </c>
       <c r="H273" t="n">
-        <v>52.93</v>
-      </c>
-      <c r="I273" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.05</v>
+      </c>
+      <c r="I273" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J273" s="9" t="n">
-        <v>0.649</v>
+        <v>0.521</v>
       </c>
       <c r="K273" s="9" t="n">
-        <v>0.645</v>
+        <v>0.527</v>
       </c>
       <c r="L273" t="inlineStr"/>
       <c r="M273" s="14" t="inlineStr"/>
@@ -12829,39 +12829,39 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>7198</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>DPS</t>
+          <t>HLBANK</t>
         </is>
       </c>
       <c r="D274" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E274" s="17" t="n">
-        <v>0</v>
+        <v>23.2</v>
+      </c>
+      <c r="E274" s="10" t="n">
+        <v>-0.0077</v>
       </c>
       <c r="F274" s="11" t="n">
-        <v>608700</v>
+        <v>604000</v>
       </c>
       <c r="G274" s="12" t="n">
-        <v>1.59</v>
+        <v>0.9</v>
       </c>
       <c r="H274" t="n">
-        <v>47.05</v>
-      </c>
-      <c r="I274" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.05</v>
+      </c>
+      <c r="I274" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J274" s="9" t="n">
-        <v>0.521</v>
+        <v>23.206</v>
       </c>
       <c r="K274" s="9" t="n">
-        <v>0.527</v>
+        <v>22.796</v>
       </c>
       <c r="L274" t="inlineStr"/>
       <c r="M274" s="14" t="inlineStr"/>
@@ -12874,39 +12874,39 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>0099</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>HLBANK</t>
+          <t>SCICOM</t>
         </is>
       </c>
       <c r="D275" s="9" t="n">
-        <v>23.2</v>
+        <v>2.33</v>
       </c>
       <c r="E275" s="10" t="n">
-        <v>-0.0077</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F275" s="11" t="n">
-        <v>604000</v>
+        <v>588100</v>
       </c>
       <c r="G275" s="12" t="n">
         <v>0.9</v>
       </c>
       <c r="H275" t="n">
-        <v>51.05</v>
-      </c>
-      <c r="I275" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.65</v>
+      </c>
+      <c r="I275" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J275" s="9" t="n">
-        <v>23.206</v>
+        <v>2.269</v>
       </c>
       <c r="K275" s="9" t="n">
-        <v>22.796</v>
+        <v>2.126</v>
       </c>
       <c r="L275" t="inlineStr"/>
       <c r="M275" s="14" t="inlineStr"/>
@@ -12919,39 +12919,39 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>0099</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>SCICOM</t>
+          <t>BIMB</t>
         </is>
       </c>
       <c r="D276" s="9" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="E276" s="10" t="n">
-        <v>-0.008500000000000001</v>
+        <v>2.07</v>
+      </c>
+      <c r="E276" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F276" s="11" t="n">
-        <v>588100</v>
+        <v>568200</v>
       </c>
       <c r="G276" s="12" t="n">
-        <v>0.9</v>
+        <v>0.43</v>
       </c>
       <c r="H276" t="n">
-        <v>59.65</v>
-      </c>
-      <c r="I276" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.86</v>
+      </c>
+      <c r="I276" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J276" s="9" t="n">
-        <v>2.269</v>
+        <v>2.087</v>
       </c>
       <c r="K276" s="9" t="n">
-        <v>2.126</v>
+        <v>2.115</v>
       </c>
       <c r="L276" t="inlineStr"/>
       <c r="M276" s="14" t="inlineStr"/>
@@ -12964,39 +12964,39 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>BIMB</t>
+          <t>SAM</t>
         </is>
       </c>
       <c r="D277" s="9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="E277" s="17" t="n">
-        <v>0</v>
+        <v>4.09</v>
+      </c>
+      <c r="E277" s="10" t="n">
+        <v>-0.0168</v>
       </c>
       <c r="F277" s="11" t="n">
-        <v>568200</v>
+        <v>558600</v>
       </c>
       <c r="G277" s="12" t="n">
-        <v>0.43</v>
+        <v>0.64</v>
       </c>
       <c r="H277" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="I277" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.52</v>
+      </c>
+      <c r="I277" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J277" s="9" t="n">
-        <v>2.087</v>
+        <v>4.24</v>
       </c>
       <c r="K277" s="9" t="n">
-        <v>2.115</v>
+        <v>4.373</v>
       </c>
       <c r="L277" t="inlineStr"/>
       <c r="M277" s="14" t="inlineStr"/>
@@ -13009,28 +13009,28 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>9822</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>SAM</t>
+          <t>AEON</t>
         </is>
       </c>
       <c r="D278" s="9" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="E278" s="10" t="n">
-        <v>-0.0168</v>
+        <v>0.965</v>
+      </c>
+      <c r="E278" s="16" t="n">
+        <v>0.0105</v>
       </c>
       <c r="F278" s="11" t="n">
-        <v>558600</v>
+        <v>547900</v>
       </c>
       <c r="G278" s="12" t="n">
-        <v>0.64</v>
+        <v>0.54</v>
       </c>
       <c r="H278" t="n">
-        <v>42.52</v>
+        <v>32.26</v>
       </c>
       <c r="I278" s="13" t="inlineStr">
         <is>
@@ -13038,10 +13038,10 @@
         </is>
       </c>
       <c r="J278" s="9" t="n">
-        <v>4.24</v>
+        <v>0.986</v>
       </c>
       <c r="K278" s="9" t="n">
-        <v>4.373</v>
+        <v>1.019</v>
       </c>
       <c r="L278" t="inlineStr"/>
       <c r="M278" s="14" t="inlineStr"/>
@@ -13054,28 +13054,28 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>AEON</t>
+          <t>LWSABAH</t>
         </is>
       </c>
       <c r="D279" s="9" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="E279" s="16" t="n">
-        <v>0.0105</v>
+        <v>1.77</v>
+      </c>
+      <c r="E279" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F279" s="11" t="n">
-        <v>547900</v>
+        <v>546300</v>
       </c>
       <c r="G279" s="12" t="n">
-        <v>0.54</v>
+        <v>0.39</v>
       </c>
       <c r="H279" t="n">
-        <v>32.26</v>
+        <v>62.7</v>
       </c>
       <c r="I279" s="13" t="inlineStr">
         <is>
@@ -13083,10 +13083,10 @@
         </is>
       </c>
       <c r="J279" s="9" t="n">
-        <v>0.986</v>
+        <v>1.697</v>
       </c>
       <c r="K279" s="9" t="n">
-        <v>1.019</v>
+        <v>1.601</v>
       </c>
       <c r="L279" t="inlineStr"/>
       <c r="M279" s="14" t="inlineStr"/>
@@ -13099,28 +13099,28 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5235SS</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>LWSABAH</t>
+          <t>KLCC</t>
         </is>
       </c>
       <c r="D280" s="9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="E280" s="17" t="n">
-        <v>0</v>
+        <v>8.35</v>
+      </c>
+      <c r="E280" s="16" t="n">
+        <v>0.0097</v>
       </c>
       <c r="F280" s="11" t="n">
-        <v>546300</v>
+        <v>540500</v>
       </c>
       <c r="G280" s="12" t="n">
-        <v>0.39</v>
+        <v>0.64</v>
       </c>
       <c r="H280" t="n">
-        <v>62.7</v>
+        <v>40.23</v>
       </c>
       <c r="I280" s="13" t="inlineStr">
         <is>
@@ -13128,10 +13128,10 @@
         </is>
       </c>
       <c r="J280" s="9" t="n">
-        <v>1.697</v>
+        <v>8.448</v>
       </c>
       <c r="K280" s="9" t="n">
-        <v>1.601</v>
+        <v>8.577</v>
       </c>
       <c r="L280" t="inlineStr"/>
       <c r="M280" s="14" t="inlineStr"/>
@@ -13144,39 +13144,39 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>5235SS</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>KLCC</t>
+          <t>KLK</t>
         </is>
       </c>
       <c r="D281" s="9" t="n">
-        <v>8.35</v>
-      </c>
-      <c r="E281" s="16" t="n">
-        <v>0.0097</v>
+        <v>22.5</v>
+      </c>
+      <c r="E281" s="10" t="n">
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F281" s="11" t="n">
-        <v>540500</v>
+        <v>537100</v>
       </c>
       <c r="G281" s="12" t="n">
-        <v>0.64</v>
+        <v>0.46</v>
       </c>
       <c r="H281" t="n">
-        <v>40.23</v>
-      </c>
-      <c r="I281" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.78</v>
+      </c>
+      <c r="I281" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J281" s="9" t="n">
-        <v>8.448</v>
+        <v>22.397</v>
       </c>
       <c r="K281" s="9" t="n">
-        <v>8.577</v>
+        <v>21.822</v>
       </c>
       <c r="L281" t="inlineStr"/>
       <c r="M281" s="14" t="inlineStr"/>
@@ -13189,39 +13189,39 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2445</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>KLK</t>
+          <t>SOP</t>
         </is>
       </c>
       <c r="D282" s="9" t="n">
-        <v>22.5</v>
+        <v>5.85</v>
       </c>
       <c r="E282" s="10" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0394</v>
       </c>
       <c r="F282" s="11" t="n">
-        <v>537100</v>
+        <v>512400</v>
       </c>
       <c r="G282" s="12" t="n">
-        <v>0.46</v>
+        <v>0.82</v>
       </c>
       <c r="H282" t="n">
-        <v>54.78</v>
-      </c>
-      <c r="I282" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.74</v>
+      </c>
+      <c r="I282" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J282" s="9" t="n">
-        <v>22.397</v>
+        <v>5.927</v>
       </c>
       <c r="K282" s="9" t="n">
-        <v>21.822</v>
+        <v>5.508</v>
       </c>
       <c r="L282" t="inlineStr"/>
       <c r="M282" s="14" t="inlineStr"/>
@@ -13234,28 +13234,28 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>SOP</t>
+          <t>MKH</t>
         </is>
       </c>
       <c r="D283" s="9" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="E283" s="10" t="n">
-        <v>-0.0394</v>
+        <v>1.99</v>
+      </c>
+      <c r="E283" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F283" s="11" t="n">
-        <v>512400</v>
+        <v>503900</v>
       </c>
       <c r="G283" s="12" t="n">
-        <v>0.82</v>
+        <v>0.42</v>
       </c>
       <c r="H283" t="n">
-        <v>50.74</v>
+        <v>65.8</v>
       </c>
       <c r="I283" s="13" t="inlineStr">
         <is>
@@ -13263,10 +13263,10 @@
         </is>
       </c>
       <c r="J283" s="9" t="n">
-        <v>5.927</v>
+        <v>1.988</v>
       </c>
       <c r="K283" s="9" t="n">
-        <v>5.508</v>
+        <v>1.979</v>
       </c>
       <c r="L283" t="inlineStr"/>
       <c r="M283" s="14" t="inlineStr"/>
@@ -13279,90 +13279,45 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>MKH</t>
+          <t>AFFIN</t>
         </is>
       </c>
       <c r="D284" s="9" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="E284" s="17" t="n">
-        <v>0</v>
+        <v>2.04</v>
+      </c>
+      <c r="E284" s="16" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F284" s="11" t="n">
-        <v>503900</v>
+        <v>503700</v>
       </c>
       <c r="G284" s="12" t="n">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="H284" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="I284" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.58</v>
+      </c>
+      <c r="I284" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J284" s="9" t="n">
-        <v>1.988</v>
+        <v>2.046</v>
       </c>
       <c r="K284" s="9" t="n">
-        <v>1.979</v>
+        <v>2.136</v>
       </c>
       <c r="L284" t="inlineStr"/>
       <c r="M284" s="14" t="inlineStr"/>
     </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>5185</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>AFFIN</t>
-        </is>
-      </c>
-      <c r="D285" s="9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="E285" s="16" t="n">
-        <v>0.009899999999999999</v>
-      </c>
-      <c r="F285" s="11" t="n">
-        <v>503700</v>
-      </c>
-      <c r="G285" s="12" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="H285" t="n">
-        <v>42.58</v>
-      </c>
-      <c r="I285" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J285" s="9" t="n">
-        <v>2.046</v>
-      </c>
-      <c r="K285" s="9" t="n">
-        <v>2.136</v>
-      </c>
-      <c r="L285" t="inlineStr"/>
-      <c r="M285" s="14" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M285"/>
+  <autoFilter ref="A1:M284"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-09-23/bursa-report-2026-09-23.xlsx
+++ b/docs/downloads/2026-09-23/bursa-report-2026-09-23.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价1.69低于50日均线1.73，RSI 54.6处中性区间，未超买；EMA20与SAR多头及T3突破信号偏积极，但均线位置显示上方仍有压力。</t>
+          <t>现价1.69低于50日均线1.73，RSI 54.6处中性区间，未超买；EMA20与SAR多头信号与均线位置略有背离，可靠性一般。</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>RSI达75.95，处超买区；现价0.59高于50日均线0.487约21%，EMA20与SAR多头信号一致，但短线偏热。</t>
+          <t>现价0.59高于50日均线0.487，EMA20与SAR均呈多头，但RSI达75.95，已进入超买区，信号可靠性需谨慎看待。</t>
         </is>
       </c>
     </row>
